--- a/TestProject/ExcelTest.xlsx
+++ b/TestProject/ExcelTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MokrinskiyA\source\repos\MSOfficeTemplateReport\TestProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25EBD9E6-C80D-4FC8-82BF-EA5E729C7D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09A14A57-6E95-4A2B-A8B4-1C82D77C6728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43695" yWindow="1470" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,6 +61,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -119,10 +122,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -437,13 +440,13 @@
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>8</v>
       </c>
     </row>
